--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.3968590963289</v>
+        <v>7.539489603153447</v>
       </c>
       <c r="D2" t="n">
-        <v>44.497854758777</v>
+        <v>7.230901398301262</v>
       </c>
       <c r="E2" t="n">
-        <v>4.64391357415326</v>
+        <v>0.7546359557999045</v>
       </c>
       <c r="F2" t="n">
-        <v>3.685035346756941</v>
+        <v>0.5988182438480028</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.10903194802238</v>
+        <v>6.030217691553638</v>
       </c>
       <c r="D3" t="n">
-        <v>37.12778406526311</v>
+        <v>6.033264910605256</v>
       </c>
       <c r="E3" t="n">
-        <v>4.64391357415326</v>
+        <v>0.7546359557999045</v>
       </c>
       <c r="F3" t="n">
-        <v>3.685035346756941</v>
+        <v>0.5988182438480028</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
